--- a/202505_resultados/ 2022 _tabela_tefm.xlsx
+++ b/202505_resultados/ 2022 _tabela_tefm.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">UF</t>
   </si>
@@ -36,12 +36,6 @@
   </si>
   <si>
     <t xml:space="preserve">[45,50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[50,55)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[55,60)</t>
   </si>
   <si>
     <t xml:space="preserve">RO</t>
@@ -476,16 +470,10 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="n">
         <v>0.003</v>
@@ -508,16 +496,10 @@
       <c r="H2" t="n">
         <v>0.004</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
         <v>0.004</v>
@@ -540,16 +522,10 @@
       <c r="H3" t="n">
         <v>0.005</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" t="n">
         <v>0.007</v>
@@ -572,16 +548,10 @@
       <c r="H4" t="n">
         <v>0.007</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" t="n">
         <v>0.008</v>
@@ -604,16 +574,10 @@
       <c r="H5" t="n">
         <v>0.01</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="n">
         <v>0.003</v>
@@ -636,16 +600,10 @@
       <c r="H6" t="n">
         <v>0.004</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
         <v>0.005</v>
@@ -668,16 +626,10 @@
       <c r="H7" t="n">
         <v>0.012</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" t="n">
         <v>0.006</v>
@@ -700,16 +652,10 @@
       <c r="H8" t="n">
         <v>0.003</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
         <v>0.003</v>
@@ -732,16 +678,10 @@
       <c r="H9" t="n">
         <v>0.003</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" t="n">
         <v>0.006</v>
@@ -764,16 +704,10 @@
       <c r="H10" t="n">
         <v>0.003</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="n">
         <v>0.002</v>
@@ -796,16 +730,10 @@
       <c r="H11" t="n">
         <v>0.002</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" t="n">
         <v>0.003</v>
@@ -828,16 +756,10 @@
       <c r="H12" t="n">
         <v>0.004</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" t="n">
         <v>0.003</v>
@@ -860,16 +782,10 @@
       <c r="H13" t="n">
         <v>0.003</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14" t="n">
         <v>0.02</v>
@@ -892,16 +808,10 @@
       <c r="H14" t="n">
         <v>0.002</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" t="n">
         <v>0.003</v>
@@ -924,16 +834,10 @@
       <c r="H15" t="n">
         <v>0.002</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B16" t="n">
         <v>0.01</v>
@@ -956,16 +860,10 @@
       <c r="H16" t="n">
         <v>0.004</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" t="n">
         <v>0.004</v>
@@ -988,16 +886,10 @@
       <c r="H17" t="n">
         <v>0.004</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B18" t="n">
         <v>0.004</v>
@@ -1020,16 +912,10 @@
       <c r="H18" t="n">
         <v>0.006</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B19" t="n">
         <v>0.004</v>
@@ -1052,16 +938,10 @@
       <c r="H19" t="n">
         <v>0.005</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B20" t="n">
         <v>0.008</v>
@@ -1084,16 +964,10 @@
       <c r="H20" t="n">
         <v>0.006</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B21" t="n">
         <v>0.005</v>
@@ -1116,16 +990,10 @@
       <c r="H21" t="n">
         <v>0.006</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B22" t="n">
         <v>0.007</v>
@@ -1148,16 +1016,10 @@
       <c r="H22" t="n">
         <v>0.008</v>
       </c>
-      <c r="I22" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B23" t="n">
         <v>0.004</v>
@@ -1180,16 +1042,10 @@
       <c r="H23" t="n">
         <v>0.006</v>
       </c>
-      <c r="I23" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B24" t="n">
         <v>0.006</v>
@@ -1212,16 +1068,10 @@
       <c r="H24" t="n">
         <v>0.009</v>
       </c>
-      <c r="I24" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B25" t="n">
         <v>0.013</v>
@@ -1244,16 +1094,10 @@
       <c r="H25" t="n">
         <v>0.009</v>
       </c>
-      <c r="I25" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.002</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B26" t="n">
         <v>0.004</v>
@@ -1276,16 +1120,10 @@
       <c r="H26" t="n">
         <v>0.003</v>
       </c>
-      <c r="I26" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B27" t="n">
         <v>0.003</v>
@@ -1308,16 +1146,10 @@
       <c r="H27" t="n">
         <v>0.004</v>
       </c>
-      <c r="I27" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B28" t="n">
         <v>0.009</v>
@@ -1339,12 +1171,6 @@
       </c>
       <c r="H28" t="n">
         <v>0.007</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.002</v>
       </c>
     </row>
   </sheetData>
